--- a/report-005-manual-005.xlsx
+++ b/report-005-manual-005.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "506c902d7590989f8b7b5fd7f29c89ba31ca9a2f", "fix_commit": "edb204625c6b6afe9afbe4d71c0783760e65b7fc", "fix_passed": true, "red_failed": true, "test_commit": "b7caae4d5a91a299de6cc333ba4416bc8a5f1383"}</t>
+          <t>{"post_fix": {"commit": "edb204625c6b6afe9afbe4d71c0783760e65b7fc", "result": "green", "trajectory_url": "未生成"}, "pre_fix": {"commit": "b7caae4d5a91a299de6cc333ba4416bc8a5f1383", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
